--- a/public/downloads/disability-welfare.xlsx
+++ b/public/downloads/disability-welfare.xlsx
@@ -4,19 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="A、權益保障" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="B、適性照顧與支持" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="C、行政管理" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="D、服務管理" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="E、員工管理與福利" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="F、會計與財務管理" state="visible" r:id="rId9"/>
+    <sheet sheetId="1" name="一、行政組織及經營管理（含會計及財務管理）" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="二、環境設施及安全維護" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="三、專業服務" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="159">
   <si>
     <t>身心障礙福利機構評鑑自我檢核表</t>
   </si>
@@ -42,20 +39,19 @@
     <t>備註</t>
   </si>
   <si>
-    <t>A、權益保障</t>
+    <t>一、行政組織及經營管理（含會計及財務管理）</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>生存權</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有保障服務對象生存權之相關規定，並確實執行
-2. 服務對象生活所需之食、衣、住、行等基本需求均獲得適當滿足
-3. 服務對象之飲食符合個別化需求（含特殊飲食、過敏等），且有書面紀錄
-4. 服務對象之居住空間安全、舒適，符合法規標準
-5. 服務對象獲得必要之醫療照護，機構建有緊急醫療處理流程</t>
+    <t>董（理）事會議會務執行及決策管理機制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 應依捐助章程或組織章程規定，執行會務(包括改選董(理)監事、財產變更登記等)，並函報主管機關。
+2. 應依捐助章程或組織章程規定期限，定期召開會議，並函報主管機關。
+3. 應於年度開始後1個月內，將其當年工作計畫及經費預算；年度結束後5個月內，將其前1年度工作報告及財務報表，提請董(理)事會通過，並函報主管機關。
+4. 法人組織對機構營運有適當之支援，如經費、行政作業、專業服務等運作之協助，並有具體資料可資說明。</t>
   </si>
   <si>
     <t/>
@@ -64,401 +60,565 @@
     <t>2</t>
   </si>
   <si>
-    <t>健康權</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象定期接受健康檢查，結果有紀錄且依需求轉介醫療
-2. 機構訂有健康管理計畫，並依個別需求提供醫療或復健服務
-3. 工作人員具備基本健康照護知能，能辨識服務對象健康異常並即時處置</t>
+    <t>機構管理制度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 應定期（至少每2個月）召開會議，會議內容應與服務有關，如服務品質改善及工作檢討等議題，並對會議決議事項需有執行及追蹤管考機制。
+2. 應訂定工作手冊（紙本或電子檔），內容應明列機構組織架構、各單位及人員業務執掌、服務對象入出機構辦法、疑似性侵害事件處理原則、重要工作流程、緊急事件求助與通報聯繫窗口、電話等資料，並落實執行。
+3. 應訂定員工權益相關制度，內容應包括員工差假、薪資給付、退休撫卹、意見反應及申訴、考核及勞動健康之辦理…等，並落實執行。
+4. 應訂有入出機構管理辦法【私立機構應依立案許可之規定，公設民營依契約規定】，辦法之內容應包含：服務對象、入出機構流程、評估機制、服務項目、收費標準等5項以上，並落實實執行。</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>得到安全的權利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有服務對象人身安全保護措施，無身體虐待、情緒虐待、性虐待等情事
-2. 機構訂有緊急事件通報流程，工作人員熟知並確實執行
-3. 服務對象如遭受不當對待，機構有明確申訴管道及保護機制
-4. 機構環境無障礙且定期維護，降低跌倒、燙傷等意外風險
-5. 服務對象之財物、文件受到妥善保管</t>
+    <t>機構配合情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 機構應配合主管機關業務輔導與發展及個案服務之需，參與相關活動、配合方案開辦、接受個案轉介與緊急安置等確實落實執行。
+2. 機構應登打「全國身心障礙福利資訊整合平台-身心障礙福利機構管理系統」並定期更新。
+3. 依據「身心障礙福利機構疑似侵害事件處理原則」第6點規定執行查閱員工有無性侵害犯罪加害人登記資料，並落實執行、如有主動提供警察刑事紀錄證明書（即良民證）亦可。
+4. 實際服務人數應達主管機關核定服務人數80%(扣除緊急安置床位)。</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>選擇的權利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象有權參與自身服務計畫之擬定，並表達意見與偏好
-2. 機構提供服務對象選擇之機會（如飲食、活動、作息等），並有書面紀錄
-3. 服務對象的選擇與決定受到尊重，工作人員不得強迫或替代決定
-4. 服務對象有能力協助下，由服務對象自行決定日常生活事務</t>
+    <t>員工健康檢查情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 員工應每2年接受健康檢查，檢查項目應包含：血液、尿液及胸部X光檢查。
+2. 新進人員應於到職前接受健康檢查，健檢項目應包含：上述各項及糞便檢查（阿米巴痢疾、桿菌性痢疾及寄生蟲），並以3個月之健檢報告為有效報告。
+3. 廚工或負責夜間之工作人員應每年接受健康檢查，檢查項目應包含血液、尿液及胸部X光檢查、A肝、傷寒、異物檢查（含阿米巴痢疾及桿菌性痢疾）。</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>隱私權</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象個人資料受到妥善保護，非必要不得外洩
-2. 機構訂有個人資料保護規定，並依個人資料保護法規定執行
-3. 服務對象之照護紀錄、健康資訊僅供有需要之工作人員查閱
-4. 執行個人照護（如沐浴、如廁）時注重隱私保護
-5. 服務對象房間有適當隱私設施，訪客管理有規定
-6. 服務對象之通訊（電話、信件等）不受無理限制
-7. 機構不得未經同意拍攝或公開服務對象之個人影像</t>
+    <t>員工訓練情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 提供新進員工職前訓練，其中應包括實際操作、授課或督導，並於到職後3個月內訓練時數應滿24小時。
+2. 每年實施員工急救訓練，內部員工參加情形達80%，另每年至少舉辦1次員工性侵害防治專業訓練，訓練以實務操作性課程為主，理論課程為輔。
+3. 直接服務人員，每人每年應接受至少20小時以上身心障礙者照顧服務相關之在職訓練，含至少4小時應急管制訓練課程及至少2小時身心障礙者口腔照護相關課程，消防演練除外。</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>參與權</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象有機會參與機構活動規劃及意見表達
-2. 機構定期舉辦服務對象會議或意見調查，並有紀錄
-3. 服務對象可自由參與社區活動，機構提供必要之協助
-4. 服務對象之宗教信仰、文化習俗受到尊重
-5. 服務對象參與自身照護計畫討論之機會有書面記載</t>
+    <t>專業服務人力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 【1106-1 社工人員】社工員之設置情形：生活重建機構-1:35。生活照顧機構-1:50。照顧人力比相除後之小數點採無條件進位，承辦特定補助方案時，應由另設單位或專屬人力辦理，不得以限定服務應有編制內人力兼辦，以免影響服務品質（如機構編制內人力兼辦者，服務總人數應符合法定規定配置比例）。應由機構提供名冊核對，比例之計算採計106-108年歷月雇用情形，予以計算後取平均值，以平均值對照計算上開標準（指標1106-1～1106-4均依本項原則）。
+2. 【1106-2 護理人員】護理人員之設置情形：全日型住宿機構1:40。照顧失智症、植物人、重癱、長期臥床或身心功能退化者為主之機構1:15。照顧需高技術性護理服務個案之機構護理人力比1:15，並應隨時至少1位護理人員值班。
+3. 【1106-3 教保員/訓練員】教保員(訓練員)設置情形：A.教保員：住宿生活照顧機構以1:3至1:7適用；夜間時段與生活服務員合併計算，與受服務人數比不得低於1:15；照顧慢性精神病患為主之機構以1:75適用職能治療師者，其教保員與受服務人員比例得以1:15適用。B.訓練員：住宿生活重建機構以1:10至1:15適用；夜間時段視需要配置訓練員。照顧慢性精神病患為主之機構以1:75適用職能治療師者，其訓練員及受服務人員比例得以1:30適用；日間生活重建機構其訓練員與受服務人員比以1:10至1:15適用。
+4. 【1106-4 生活服務員】生活服務員設置情形：住宿型生活重建機構日間時視需要配置，夜間1:10~1:15。住宿型生活照顧機構1:3~1:6，夜間時與受服務人數比不得低於1:15（夜間生活服務員與教保員得合併計算）。</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>人際社交的權利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象可自由與家人、朋友保持聯繫，機構提供必要協助
-2. 機構不得無故限制服務對象之人際交往
-3. 服務對象之親密關係與性自主受到尊重，機構有相關支持措施
-4. 機構安排適當之社交活動，促進服務對象人際互動
-5. 服務對象與外界社會之連結獲得維持與支持</t>
+    <t>法定通報責任</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 將性侵害犯罪防治法第8條、身心障礙者權益保障法第76條之通報機制納入內部流程並落實執行。
+2. 辦理或參與相關人員通報訓練及宣導教育。</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>服務意見反應與申訴權</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構設有服務對象申訴管道，並公告周知
-2. 申訴案件均有紀錄、處理及追蹤，處理結果通知申訴人
-3. 服務對象及家屬知悉申訴管道及主管機關陳情方式
-4. 機構定期辦理服務滿意度調查，結果作為服務改善依據
-5. 服務對象申訴後不得遭受不當對待或報復</t>
-  </si>
-  <si>
-    <t>B、適性照顧與支持</t>
+    <t>會計制度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 訂定健全之會計制度，且有落實，並應設置日記帳及總分類帳。
+2. 各項支出經抽核均依法取得政府規定之合法憑據（發票或收據）且支出項目及用途合理。
+3. 營運擔保金、接受各級政府機關補助款及入機構保證金，應設置專戶，足額儲存並專款專用。</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>回應個人需求與期待支持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構於服務對象入住前完成需求評估，了解個別需求與期待
-2. 評估結果有書面記錄，並作為服務計畫擬定之依據
-3. 服務對象需求變化時，適時調整服務內容
-4. 服務對象對服務之期待與目標有書面紀錄，並定期檢視達成情形</t>
+    <t>財務報告及管理作為</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 經董(理)監事會議決議或負責人認可之財務報表內容應包括資產負債表、收支餘絀表、現金流量表(現金出納表)、淨值變動表(基金收支變動表)及附註或附表。
+2. 財務報表依規定函報立案之主管機關備查。
+3. 3年度平均業務支出占支出合計≧75%。</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>個別化支持／服務計畫（ISP）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 每位服務對象均有個別化支持計畫（ISP），並由跨專業團隊共同擬定
-2. ISP 涵蓋服務對象之短期與長期目標，目標具體可量測
-3. 服務對象及家屬（監護人）參與 ISP 之擬定並簽名確認
-4. ISP 至少每6個月檢視一次，依需求調整
-5. ISP 執行情形有定期記錄，並評估目標達成程度</t>
+    <t>財物管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 經費之支出在新臺幣1萬元以上應全數開立支票或透過金融機構撥付。
+2. 印鑑由適當權責人員分別保管，有價證券應由專人管理。
+3. 有專人管理財產，應每年至少盤點1次並有紀錄。
+4. 政府補助購置財產或代管財產，均依規定編列財產清冊及財產標示（固定黏貼於財產上可供辨識處）。</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>特殊照顧支持需求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 具特殊照顧需求（如鼻胃管、導尿管、氣切等）之服務對象，有書面照護計畫
-2. 執行特殊照護之工作人員具備相關訓練，並有訓練記錄
-3. 特殊照護執行有書面紀錄，並定期評估照護成效
-4. 服務對象特殊照護需求變化時，即時通知家屬及相關專業人員</t>
+    <t>捐贈財物之管理徵信情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 應有完備之受贈財物徵信及管理規定。
+2. 開立收據予捐贈人，依規定報主管機關備查。
+3. 受贈財物之使用符合捐贈者指定用途（用途以所開立收據為準），並專簿載明收支運用情形。指定用途捐款得集中一個專戶存款，但同一專戶中性質不同之款項，應依其原定用途在存額內辦理支付，該專戶存款應足額儲存。
+4. 公開徵信：應刊登於所屬網站或發行之刊物，無網站及刊物者，應刊登於新聞紙或電子媒體，有指定用途者應予載明。</t>
+  </si>
+  <si>
+    <t>二、環境設施及安全維護</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>情緒行為支持需求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 具情緒行為支持需求之服務對象，有書面行為支持計畫
-2. 行為支持計畫以正向支持策略為主，不得使用懲罰或限制措施作為主要手段
-3. 工作人員接受正向行為支持訓練，有訓練紀錄
-4. 情緒行為事件有紀錄及追蹤，必要時調整支持策略</t>
+    <t>浴廁比例、隱密性及方便性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 浴廁與服務人數比例不得小於1:6。
+2. 主要活動空間（如活動室、教室、寢室、起居室）之樓層應設有廁所。
+3. 浴廁應符合隱密性(廁所應有男女之分，廁所應有隔間或門簾，浴室應有隔間或門簾，方符隱密性要求)。如浴廁顯然無法與他人共用時，得不另加設隔間或門簾。
+4. 【3101-B 重度失能機構適評】每60人應至少設置一套適合臥床身心障礙者使用且可操作之洗澡設備與空間(未滿60人者，以60人計)。浴廁應符合隱密性(廁所應有男女之分，廁所應有隔間或門簾，方符隱密性要求)。</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>其他多元支持需求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象之溝通、學習、休閒等多元需求獲得評估並有支持措施
-2. 必要時提供輔助溝通系統（AAC）或其他輔具
-3. 多元支持措施有書面記錄，並定期評估成效</t>
+    <t>無障礙浴廁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 以108年新公告之設計規範為依據。出入口之高差、寬度、門開關方式及地面材料止滑。
+2. 輪椅之迴轉空間、馬桶之設計與空間足供可自行使用輪椅者橫向移坐，並兩側設有扶手。
+3. 洗臉盆及鏡子。
+4. 至少有1處淋浴間可供自行使用輪椅者方便沐浴，可自行使用輪椅者每滿6人或其餘數應增設一處廁所。</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>社區資源的管理與運用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構建有社區資源清冊，並定期更新
-2. 依服務對象需求，主動連結或轉介適當社區資源
-3. 社區資源運用情形有書面紀錄
-4. 服務對象參與社區活動之機會有規劃，並有執行紀錄</t>
+    <t>緊急呼叫設備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 無障礙廁所、浴室應依無障礙設施規定設置緊急呼叫設備(救助鈴)。
+2. 寢室考量服務對象之屬性，設置適當之緊急呼叫設備，並符合服務人員方便使用，重度失能臥床者寢室每床應設置適當之緊急呼叫設備。
+3. 一般廁所、浴室考量服務對象之屬性，設置適當之緊急呼叫設備，並符合服務人員方便使用。
+4. 緊急呼叫設備功能正常。</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>家庭支持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有家庭支持服務計畫，依家庭需求提供適當支持
-2. 定期與家屬溝通，告知服務對象近況，有通聯紀錄
-3. 提供家屬照顧技能訓練或相關資訊
-4. 服務對象與家屬有定期聯繫（探視或通訊）機會，且有紀錄
-5. 家屬有參與 ISP 之機會，並受到尊重
-6. 機構提供家屬喘息或情緒支持資訊
-7. 家庭危機事件有即時通報及處理流程
-8. 家屬對服務之意見有管道反映，並獲得回應</t>
+    <t>有無避難逃生路徑及等待救援空間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 樓梯間、走道、出入口、防火門應符合無障礙之逃生路徑。安全梯出入口、防火區劃之防火門出入口等周圍1.5公尺地面須淨空。
+2. 逃生路徑為雙向（有兩個以上的逃生出口）。
+3. 逃生路徑之防火門應往避難方向開啟並隨時保持關閉，或能與火警自動警報設備連動而關閉，且不需鑰匙即可雙向開關。
+4. 設有等待救援空間，應具備通排煙及防火區劃功能。</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>轉銜支持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 服務對象離開機構（轉銜）前，有書面轉銜計畫
-2. 轉銜計畫由跨專業團隊共同擬定，並徵詢服務對象及家屬意見
-3. 轉銜過程中，機構主動協助銜接新服務單位或資源
-4. 轉銜相關文件（照護摘要、評估紀錄等）完整移交
-5. 轉銜後追蹤服務對象適應情形，有追蹤紀錄</t>
+    <t>建築物公共安全檢查簽證申報及消防安全設備設置、檢修申報及防火管理情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 依規定辦理建築物公共安全檢查簽證申報，現場置有檢查報告書及地方政府核發之審查合格證明文件。
+2. 消防安全設備每半年檢修申報1次，並備有3年內申報完整紀錄。
+3. 建立防火管理制度，適用之防火管理人應受訓取得合格證明文件，且工作人員了解自身職責。
+4. 機構應每個月自主檢查機構內部用電設備安全，且每半年1次委託用電設備檢驗維護業者定期檢驗機構所有用電設備，並皆有紀錄。</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>生涯教育與職性關懷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 依服務對象年齡與能力，提供生涯規劃相關資訊與教育
-2. 有意願就業之服務對象，獲得就業輔導或職業訓練資源連結
-3. 機構訂有職性關懷計畫，提供多元學習與發展機會
-4. 生涯教育與職性關懷執行情形有書面紀錄
-5. 服務對象之生涯目標納入 ISP，並定期追蹤</t>
-  </si>
-  <si>
-    <t>C、行政管理</t>
+    <t>訂定符合機構特性及需要之緊急災害應變計畫及作業程序，並落實演練</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 對於火災、風災、水災、地震及停電緊急災害，訂有符合機構與災害特性之緊急災害應變計畫與作業程序(含指揮架構)。
+2. 訂有防火及避難安全風險自主檢核計畫，落實執行並有紀錄。
+3. 每年應實施緊急災害應變演練至少2次以上，包括夜間演練1次，且有演練之腳本、過程、演練後之檢討會議及檢討修正之方案。</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>法規對服務對象的規定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構依「身心障礙福利機構設施及人員配置標準」設置，並符合相關法規規定
-2. 服務對象之入住資格、服務人數符合法規及主管機關核定之規定</t>
+    <t>訂定符合機構服務對象之疏散策略及持續照顧作業程序，並落實照顧人力之緊急應變能力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 機構應於各樓層出入口張貼緊急避難平面圖(或逃生圖)，明確訂定各樓層服務對象疏散數量運送之順序與策略。
+2. 緊急避難平面圖(或逃生圖)應具比例，且標示所在位置並與機構現場方向、方位符合。
+3. 安排防火管理人及其他工作人員參與災害風險辨識、溝通及防救災之教育訓練，並落實應變救援能力。</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>行政管理落實</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有組織章程、服務規定及各項行政管理制度，並公告周知
-2. 各項紀錄、報表依規定保存，查閱方便
-3. 機構定期召開行政會議，有會議紀錄
-4. 機構與主管機關保持良好溝通，按時繳交各項報表及配合訪視</t>
-  </si>
-  <si>
-    <t>D、服務管理</t>
+    <t>寢室面積及自然採光通風</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 50%以上~未達75%之寢室面積符合規定。
+2. 75%以上~未達100%之寢室面積符合規定。
+3. 寢室面積符合規定。
+4. 每間寢室都有採光及通風。</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>機構設施安全</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構建築設施符合建築、消防等相關法規，並有合格證明文件
-2. 機構設有消防安全設備，定期維護保養並有紀錄
-3. 每年至少辦理2次消防疏散演練（含夜間演練），有演練紀錄
-4. 無障礙設施符合規定，服務對象可自主使用
-5. 機構環境整潔，無安全隱患，定期環境維護有紀錄
-6. 危險物品（清潔劑、藥品等）妥善管理，防止服務對象誤取</t>
+    <t>機具使用安全及儀器設備操作維護</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 設置警示標誌（或標語）及操作說明。
+2. 有防護設備並有維護紀錄。
+3. 訂有儀器設備定期維護之相關作業規定及人員操作訓練辦法。
+4. 儀器設備有維護或定期校正之機制，以及定期盤點各類儀器設備操作技術，並有紀錄。</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>工作手冊</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有各職類工作手冊，內容含工作職責、服務流程及注意事項
-2. 工作手冊定期更新，並確保所有工作人員知悉</t>
+    <t>重度失能機構之護理空間/護理站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 護理站應有護理紀錄櫃、藥品存放櫃及護理工作車。
+2. 護理站應有護理準備空間及洗手設備(如洗手台或乾洗液)。
+3. 每棟層均設有護理站或簡易護理工作站。</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>機構風險管理處理要點</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有風險管理計畫，含意外事件、緊急事件等各類風險之預防及處理流程
-2. 風險事件發生後有書面紀錄、分析及改善措施，並定期檢討</t>
+    <t>環境清潔衛生及廢棄物處理分類</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 機構環境清潔且無異味，有具體杜絕蚊蟲害之防治措施(含實施計畫及佐證紀錄)及設施(如紗窗、紗門等)。
+2. 每3個月機構環境全面消毒1次並有紀錄。
+3. 依地方主管機關訂定之廢棄物清理相關規定進行分類，廢棄物之裝置器具應加蓋且廢棄物定時清理，定點存放且有專人處理。
+4. 事業廢棄物或感染性廢棄物之清理應與廠商訂有合約，且在有效期限內，或由合作醫院處理之相關佐證文件；事業廢棄物依規定處理且有紀錄可查。</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>服務使用者權益維護機制</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有服務使用者權益維護相關規定，並公告周知
-2. 工作人員接受服務使用者權益保護相關教育訓練，有訓練紀錄
-3. 機構定期辦理服務品質自我評估，結果作為改善依據</t>
-  </si>
-  <si>
-    <t>E、員工管理與福利</t>
+    <t>污物處理情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 訂有污物處理辦法及流程，且有處理紀錄。
+2. 污物處理及動線符合感染管控原則。</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>員工支持方案</t>
-  </si>
-  <si>
-    <t>1. 機構訂有員工支持方案，提供工作壓力疏導、員工協助方案（EAP）等相關資源，並有執行紀錄</t>
+    <t>餐廳、廚房之環境設備與餐具符合衛生原則</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 訂有廚房及配膳作業標準（至少應包含設備之清潔、檢查意、垃圾及廚餘之處理方式）。
+2. 設備（包含餐桌椅、加熱炊具、流理台等）及環境（地板、門縫、牆角、天花板、門窗）整潔，定期清理及消毒且有紀錄。廚房或配膳作業空間有防治蚊蠅、蟑螂及鼠害之適當措施（紗門、紗窗）。
+3. 供膳外包機構與廠商訂有合約且在有效期限內，並有衛生主管機關稽查、抽驗之合格證明；或提供自主管理相關文件資料（如食材或成品之自主檢驗報告、內稽或外稽等紀錄）。
+4. 餐具應有消毒設備(高溫、高壓或紫外線)，有傳染管理需求之對象應有個人專屬餐具。</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>員工職業安全</t>
-  </si>
-  <si>
-    <t>1. 機構依職業安全衛生法規定，訂有職業安全衛生管理計畫，工作人員接受職安訓練，有訓練紀錄</t>
+    <t>食物儲存空間及冷凍（藏）設備</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 有食物儲存空間及冷凍、冷藏設備，冷藏設備溫度需7℃以下。
+2. 食物儲放適當：蔬菜與魚肉類、乾貨分開儲放。
+3. 定期檢查且有紀錄(應有食物進貨日期或有效日期)。
+4. 專屬儲存空間：食品儲存空間未置放非食品。</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>員工權利</t>
-  </si>
-  <si>
-    <t>1. 機構依勞動基準法及相關法規保障員工薪資、工時、休假等基本勞動權益，無違規情事</t>
+    <t>儲藏設施設置情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 易燃或可燃性物品應集中管理，公共儲藏空間應隨時上鎖並有完整隔間。
+2. 上述公共儲藏空間各儲存物品具備分類標示並有進冊及定期盤點。</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>員工教育訓練</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有年度教育訓練計畫，涵蓋新進人員職前訓練及在職訓練，並確實執行
-2. 各職類工作人員依規定完成每年應接受之訓練時數，訓練紀錄完整</t>
+    <t>室外通路</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 室外通路之高差及寬度。
+2. 室外通路與主要通路不同時，應有引導標誌。
+3. 地面應平整、堅固、防滑且水溝格柵符合規定。
+4. 通路上之突出物。</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>員工健康檢查</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 新進員工依規定完成健康檢查，無礙於服務對象照護之健康狀況
-2. 在職員工依規定定期辦理健康檢查，結果有紀錄，必要時依法辦理工作調整</t>
+    <t>室內通路走廊及出入口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 通路走廊之寬度。
+2. 通路走廊上各出入口之高差及寬度。
+3. 通路走廊之輪椅迴轉空間。
+4. 通路走廊上之突出物。</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>員工激勵與責任落實</t>
-  </si>
-  <si>
-    <t>1. 機構訂有員工績效考核及獎懲制度，考核結果與薪資晉升連結，並定期執行考核</t>
-  </si>
-  <si>
-    <t>F、會計與財務管理</t>
+    <t>坡道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 坡道之寬度。
+2. 坡度及地面防滑。
+3. 坡道之平台。
+4. 防護設施及扶手。</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>會計與財務管理</t>
-  </si>
-  <si>
-    <t>1. 機構依法設置會計帳冊，財務報表正確完整，並依規定保存</t>
+    <t>樓梯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 梯級路面前端防滑。
+2. 梯級起點與終點之警示設施。
+3. 扶手及樓梯底板下方防護設施。</t>
   </si>
   <si>
     <t>31</t>
   </si>
   <si>
-    <t>財務管理要件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有財務管理規定，明訂授權核決、收支管理等相關流程
-2. 機構財務報告定期提交主管機關或董事會，並依規定公開揭露</t>
+    <t>昇降機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 昇降機出入口之寬度及引導設施。
+2. 昇降機前方之輪椅迴轉空間。
+3. 點字設施、標誌及輪椅乘坐者之操作盤。
+4. 扶手及後視鏡。</t>
+  </si>
+  <si>
+    <t>三、專業服務</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>現金收支管理</t>
-  </si>
-  <si>
-    <t>1. 現金收支有完整紀錄，定期核對，帳款相符</t>
+    <t>個別化服務/支持計畫之擬訂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 每年為每位服務對象進行評估、個別召開服務/支持計畫會議，並完成擬訂個別化服務/支持計畫。
+2. 新進服務對象應於2個月內（生活重建機構應於1個月）召開會議，完成個別化服務/支持計畫擬訂，並應有本人及家屬參與。（如家屬無法參與者，應列冊說明並有多元聯繫管道紀錄）
+3. 評估工具及評估方法的選用應適齡、適性。
+4. 評估過程應納入服務對象需求、興趣及本人及家屬之期待。</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>固定資產之財務管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有固定資產管理規定，建有資產清冊，定期盤點
-2. 固定資產折舊依會計原則計提，財務報表正確反映資產現值</t>
+    <t>依據評估結果擬定服務目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 評估結果應有反映服務對象現況、需求或期待的綜合摘述。
+2. 依據評估結果擬訂多元領域之服務目標。
+3. 目標應綜合考量個人或家庭之期待、轉銜需求。
+4. 計畫中包含合適的長期及短期目標，且短期服務目標應具體可行（可觀察、可評量並具功能性）。</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>物資之財務管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構訂有物資（耗材、食材等）管理規定，採購、驗收、領用均有紀錄
-2. 物資庫存定期盤點，帳物相符</t>
+    <t>服務目標之執行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 依目標擬定具體可行的服務策略或方法，必要時加以調整。
+2. 確實執行服務目標並有紀錄，至少每2週記錄1次。
+3. 應每半年至少檢討1次服務/支持計畫之執行(生活重建機構至少每3個月檢討1次)，並有紀錄。
+4. 必要時修正服務目標或服務/支持計畫，將檢討或修正之結果告知本人或家屬（或代理人），並有紀錄。</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
-    <t>成本管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 機構定期進行成本分析，了解各項服務成本結構
-2. 成本分析結果作為服務費用訂定及資源配置之參考</t>
+    <t>專業團隊服務模式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 有專業團隊合作規劃要點/規定，並依要點/規定確實執行。
+2. 應依服務對象需要邀請相關專業人員參與服務/支持計畫之擬訂與執行。
+3. 相關專業人員間應進行專業知能交流（如：個案研討、在職訓練、團隊評估…等），其中個案研討每年至少辦理2次。
+4. 督導頻率至少每月1次，督導內容包括專業知能提升及與服務對象有關之問題討論、危機預防與管理…等，並有紀錄。</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>輔具及活動器材</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 應依服務對象需求提供適性的生活輔具及活動器材，並適當運用於日常活動中（如：飲食、學習、溝通、生活、作業活動、休閒…等活動）。
+2. 相關輔具和器材的提供應具安全性及功能良好，且應定期檢查及維護，並有紀錄。
+3. 輔具應讓服務對象取拿方便（位置、高度、動線…等符合使用者特性）。
+4. 活動器材應讓服務對象取拿方便（位置、高度、動線…等符合使用者特性）。</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>特殊的支持措施</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 有行為情緒支持需求者，應提供行為觀察及支持策略，並有追蹤及執行紀錄。
+2. 配合服務對象身體健檢結果，或健康需求規劃衛教內容（如：衛生習慣、傳染病預防、手部衛生、吸嘔預防、用藥常識…等）並有執行紀錄。
+3. 配合服務對象之生理發展及人際互動需求，規劃合宜之性平教育（如：性別認識、性別尊重、隱私、交友、懷孕/避孕等）並有執行紀錄。</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>體能與休閒活動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 【4204-A 體能與休閒活動】配合服務對象體能或健康需求進行適齡適性的體能活動規劃。
+2. 【4204-A】每週至少執行體能活動2小時，並有紀錄。
+3. 【4204-A】每週規劃安排多元休閒活動。
+4. 【4204-A】休閒活動內容與進行方式應適齡、適性。
+5. 【4204-B 重度失能機構適評】提供服務對象下床及安全評估，並協助每位可移動的服務對象，每天至少下床2次，並確實執行且有紀錄；針對意識不清或昏迷的服務對象每天至少下床1次。
+6. 【4204-B】為利服務對象下床活動，應使用符合個別需求及維護身體功能之輔具。
+7. 【4204-B】照顧者依據物理/職能治療師專業評估，每日提供簡易被動式肢體活動，確實執行並有紀錄。
+8. 【4204-B】提供感官認知功能刺激活動，確實執行並有紀錄。</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>空間規劃與作息人力配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 活動空間之相關設施，應符合服務對象使用之便利性(指位置、高度、數量皆適當)。
+2. 空間規劃應有清楚的功能區隔。
+3. 服務對象每天轉換2個以上的活動空間。
+4. 應依據活動內容及時段配置相關服務人員，必要時有相關專業人員提供服務。</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>提供服務對象的清潔服務</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 每日整理服務對象之儀容，提供足夠及清潔之寢具及衣物，且每週至少洗滌（非擦澡）2次(夏天至少每2天1次)，以保持服務對象的服裝、儀容合宜且無異味。
+2. 對有可能失禁之服務對象至少每2小時協助如廁1次，並有紀錄。
+3. 觀察失禁情形並做紀錄。
+4. 對有可能控制如廁之服務對象，訓練其自行如廁計畫並有紀錄。</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>服務對象壓力性損傷預防及處理情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 訂有服務對象壓力性損傷預防評估措施、處理辦法及流程。
+2. 協助臥床服務對象，至少每2小時正確執行翻身拍背。
+3. 翻身擺位正確。
+4. 如有發生壓力性損傷案件應定期(每季)進行分析，檢討並有改善方案。</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>定期健檢，並作健康管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 6歲以上服務對象接受服務前3個月內應提供體檢文件且健檢項目完整；學齡前服務對象接受服務前應提供兒童健康手冊。
+2. 每位服務對象每年接受健康檢查，並針對個別健檢結果進行追蹤及處遇；若服務對象協助供應者，體檢項目應加做A肝及糞便。</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>口腔照護支持服務</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 每位服務對象每年至少1次口腔檢查。
+2. 視需要安排口腔照護支持服務（如：塗氟、洗牙、治療等）並保留相關服務紀錄。</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>膳食服務</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 【4303-A 膳食服務】依服務對象生活習慣或宗教因素提供不同類型食物(如：素食者或特殊禁忌)。
+2. 【4303-A】膳食設計符合營養師之建議並有紀錄，菜色有變化且至少15天不重複。
+3. 【4303-A】每道食物檢體（至少200公克）應獨立盛裝，並標示日期及餐次，冷藏保存48小時後始得丟棄。
+4. 【4303-A】依服務對象之特殊生理狀況(如：糖尿病、腎臟病、心臟病、肥胖、痛風或吞嚥能力等)提供個別化飲食，含不同食物質地(如：一般飲食、細碎、軟食、流質、管灌等)。
+5. 【4303-B 管灌服務對象餵食情形（重度失能機構適評）】管灌服務對象有個別之灌食空針，使用過程符合衛生清潔原則。
+6. 【4303-B】灌食配方成分、份量與溫度適合服務對象個別需要。
+7. 【4303-B】灌食技術正確(管路位置確認，回抽，空針高度正確，流速適當)，且無食物或藥物殘留，灌食管路維持暢通。
+8. 【4303-B】灌食時及灌食後注意服務對象需求與感受(姿勢維持如1小時內，頭頸部抬高30至45度；管灌時對服務對象說明或打招呼)。</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>用藥及托藥安全管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 依醫囑或托藥單給藥且藥物未逾使用期限，並有給藥紀錄。
+2. 藥物放置地點適當且安全(如儲櫃或門上鎖)，藥物盒裝有清楚標示姓名及服用時間。</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>意外傷害或緊急事件處理情形</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 訂有處理要點／規定（含：紀錄表單、處理流程、緊急聯絡管道）並確實執行。
+2. 處理過程應有紀錄，且包含檢討、改善方案或預防措施，並有追蹤紀錄。</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>傳染病之預防與處理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 每日監視紀錄服務對象與工作人員之體溫健康狀況，且有完整紀錄，並依「人口密集機構傳染病防治及監視作業注意事項」規定執行疫情監視及上網登錄通報。
+2. 訂定傳染病（包括呼吸道傳染病、腸道傳染病、不明原因發燒及群聚感染等）之預防及處理措施並確實執行，於發生傳染病事件有處理過程紀錄，且能分析檢討，並有改善方案或預防措施。
+3. 落實手部衛生作業及稽核。</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>社區資源管理與運用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 建立多元之社區相關資源網絡（如：志工人力、醫療、轉銜、轉介、福利及經濟補助資源…等）並留有資源運用紀錄，且每年至少1次盤點更新。
+2. 每位服務對象每月至少1次外出參與社區活動（無法參與者應列冊說明原因），應服務對象需求或意願規劃並留有執行紀錄。
+3. 服務對象如有交通需求，應結合社區資源、協助其交通並建立協助機制(如協助申請交通費補助、安排交通車接送、代訂無障礙計程車等)。</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>家庭訪視與需求評估</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 新進服務對象應於2個月內完成家庭訪視，且有訪視紀錄。之後每2年至少1次家庭訪視，且有訪視紀錄。
+2. 針對每位成人服務對象進行家庭評估，但依服務對象之需求及意願擬訂家庭支持/服務計畫及紀錄；針對每位學齡(前)服務對象進行家庭需求評估，並綜合摘述。
+3. 每年應重新評估。</t>
   </si>
 </sst>
 </file>
@@ -878,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -934,7 +1094,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -957,7 +1117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -980,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -1003,7 +1163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
@@ -1026,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="112" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -1049,7 +1209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
@@ -1072,7 +1232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
@@ -1095,7 +1255,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -1115,6 +1275,75 @@
         <v>12</v>
       </c>
       <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1130,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1177,7 +1406,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1188,13 +1417,13 @@
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -1209,15 +1438,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -1234,13 +1463,13 @@
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -1257,13 +1486,13 @@
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -1278,15 +1507,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -1301,15 +1530,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -1324,15 +1553,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="128" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -1347,15 +1576,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>12</v>
@@ -1370,15 +1599,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -1390,6 +1619,259 @@
         <v>12</v>
       </c>
       <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1405,7 +1887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1452,7 +1934,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1461,15 +1943,15 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -1486,13 +1968,13 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -1507,129 +1989,15 @@
         <v>12</v>
       </c>
     </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="62" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="96" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -1644,15 +2012,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -1667,175 +2035,15 @@
         <v>12</v>
       </c>
     </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="62" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -1850,15 +2058,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -1873,209 +2081,279 @@
         <v>12</v>
       </c>
     </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="62" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="5" t="s">
+    <row r="10" ht="128" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="128" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>12</v>
       </c>
     </row>
